--- a/Data/EXCEL/Transfer/salemon/202208/6705-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6705-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40C63285-DA8D-485F-9775-37032ADFC99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E15576AD-338A-401D-9B00-9A8728EB31C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6705-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,18 +1227,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q53"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="5" width="9.625" customWidth="1"/>
-    <col min="6" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="11" width="9.625" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="16" width="9.625" customWidth="1"/>
-    <col min="17" max="17" width="9.375" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="13.375" customWidth="1"/>
+    <col min="13" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1265,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1296,7 +1304,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1339,7 +1347,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1378,7 +1386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1431,7 +1439,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1484,7 +1492,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1537,7 +1545,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1590,7 +1598,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1643,7 +1651,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1696,7 +1704,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1749,7 +1757,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1802,7 +1810,7 @@
         <v>59.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1855,7 +1863,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1908,7 +1916,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1961,7 +1969,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2014,7 +2022,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2067,7 +2075,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2120,7 +2128,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2173,7 +2181,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2226,7 +2234,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2279,7 +2287,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2332,7 +2340,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2385,7 +2393,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2438,7 +2446,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2491,7 +2499,7 @@
         <v>-25.1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2544,7 +2552,7 @@
         <v>-27.1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2597,7 +2605,7 @@
         <v>-27.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2650,7 +2658,7 @@
         <v>-26.3</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2703,7 +2711,7 @@
         <v>-26.9</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2756,7 +2764,7 @@
         <v>-25.1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2809,7 +2817,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2862,7 +2870,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2915,7 +2923,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2968,7 +2976,7 @@
         <v>-3.48</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3021,7 +3029,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3074,7 +3082,7 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3127,7 +3135,7 @@
         <v>-6.44</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3180,7 +3188,7 @@
         <v>-7.32</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3233,7 +3241,7 @@
         <v>-5.26</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3286,7 +3294,7 @@
         <v>-6.72</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3339,7 +3347,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3392,7 +3400,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3445,7 +3453,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3498,7 +3506,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3551,7 +3559,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3604,7 +3612,7 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3657,7 +3665,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3710,7 +3718,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3763,7 +3771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3816,7 +3824,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3869,7 +3877,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3922,7 +3930,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3990,7 +3998,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>